--- a/data/trans_dic/P20B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 66,06</t>
+          <t>8,1; 65,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 58,06</t>
+          <t>8,17; 58,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 58,86</t>
+          <t>0,0; 52,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,61</t>
+          <t>0,0; 22,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 23,74</t>
+          <t>2,91; 28,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,4</t>
+          <t>0,0; 22,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,84</t>
+          <t>0,0; 57,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 23,44</t>
+          <t>2,43; 22,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 29,93</t>
+          <t>8,54; 31,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 25,61</t>
+          <t>4,56; 26,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,59</t>
+          <t>0,0; 49,27</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 47,67</t>
+          <t>9,94; 43,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 36,18</t>
+          <t>6,13; 35,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,69</t>
+          <t>0,0; 44,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 71,03</t>
+          <t>6,65; 70,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 16,28</t>
+          <t>2,74; 16,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,23</t>
+          <t>2,21; 12,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,93</t>
+          <t>3,04; 16,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,73</t>
+          <t>0,0; 27,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 20,03</t>
+          <t>6,64; 19,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 15,27</t>
+          <t>4,76; 14,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 16,66</t>
+          <t>3,76; 16,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 28,43</t>
+          <t>5,34; 30,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,26; 61,3</t>
+          <t>16,88; 61,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,22; 53,44</t>
+          <t>18,39; 52,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,62; 65,91</t>
+          <t>23,03; 66,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 49,14</t>
+          <t>7,72; 47,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 36,38</t>
+          <t>7,88; 33,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,16; 46,19</t>
+          <t>18,63; 44,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 29,94</t>
+          <t>7,31; 29,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,01; 36,12</t>
+          <t>12,16; 36,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,43; 38,11</t>
+          <t>15,59; 37,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,28; 42,1</t>
+          <t>22,71; 43,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 35,64</t>
+          <t>15,77; 37,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,78; 33,76</t>
+          <t>14,44; 35,48</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 36,91</t>
+          <t>4,32; 38,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,43; 60,69</t>
+          <t>24,91; 59,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 63,51</t>
+          <t>23,28; 67,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,07; 56,05</t>
+          <t>22,35; 54,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,71; 60,87</t>
+          <t>19,42; 57,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,55; 63,88</t>
+          <t>36,11; 64,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,72; 65,06</t>
+          <t>26,97; 65,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,88; 57,53</t>
+          <t>29,58; 57,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,82; 41,76</t>
+          <t>16,84; 40,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,79; 58,27</t>
+          <t>36,1; 57,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,42; 59,91</t>
+          <t>31,25; 58,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,32; 51,65</t>
+          <t>28,9; 51,87</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,5; 69,86</t>
+          <t>24,97; 65,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 53,31</t>
+          <t>18,4; 52,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,31; 66,03</t>
+          <t>26,26; 64,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,17; 49,91</t>
+          <t>24,23; 51,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,34; 67,06</t>
+          <t>28,01; 68,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,05; 61,02</t>
+          <t>22,94; 60,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,2; 70,18</t>
+          <t>27,34; 69,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,86; 43,2</t>
+          <t>17,71; 43,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,24; 62,51</t>
+          <t>32,35; 61,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,33; 49,98</t>
+          <t>23,96; 50,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,61; 60,58</t>
+          <t>36,64; 61,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,76; 43,79</t>
+          <t>25,03; 44,61</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 45,58</t>
+          <t>7,81; 45,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,99; 53,29</t>
+          <t>18,2; 55,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,17; 39,05</t>
+          <t>11,89; 40,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,47; 55,41</t>
+          <t>28,46; 54,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 52,55</t>
+          <t>18,21; 49,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,59; 50,83</t>
+          <t>18,22; 50,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,98; 64,38</t>
+          <t>25,66; 64,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,79; 34,85</t>
+          <t>11,55; 36,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,87; 41,01</t>
+          <t>17,38; 41,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,45; 45,46</t>
+          <t>22,62; 47,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,46; 45,6</t>
+          <t>22,52; 46,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,55; 43,66</t>
+          <t>24,79; 43,57</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 34,61</t>
+          <t>4,22; 35,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 36,47</t>
+          <t>5,74; 38,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,78; 47,82</t>
+          <t>10,33; 46,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,71; 34,85</t>
+          <t>10,47; 34,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 35,09</t>
+          <t>6,56; 33,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 28,13</t>
+          <t>7,07; 29,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,35; 44,4</t>
+          <t>12,28; 43,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 34,24</t>
+          <t>15,91; 34,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 28,2</t>
+          <t>7,47; 27,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,61; 26,61</t>
+          <t>9,3; 27,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,45; 40,2</t>
+          <t>16,33; 39,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,43; 30,4</t>
+          <t>16,28; 30,43</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,86; 34,1</t>
+          <t>19,5; 34,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,14; 37,79</t>
+          <t>23,73; 37,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,16; 40,84</t>
+          <t>25,74; 41,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,4; 39,67</t>
+          <t>26,82; 39,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,34</t>
+          <t>14,8; 25,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,77; 29,43</t>
+          <t>19,95; 29,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,62</t>
+          <t>18,85; 30,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,29; 27,91</t>
+          <t>18,49; 28,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,69</t>
+          <t>18,71; 26,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,13; 30,62</t>
+          <t>22,6; 30,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23,44; 32,62</t>
+          <t>23,71; 32,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,49; 31,91</t>
+          <t>23,75; 32,09</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>845; 6686</t>
+          <t>820; 6649</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1224; 8598</t>
+          <t>1211; 8734</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>988; 7262</t>
+          <t>0; 6527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1122</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4141</t>
+          <t>0; 6261</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>981; 8357</t>
+          <t>1023; 9923</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8041</t>
+          <t>0; 7536</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 13233</t>
+          <t>0; 12777</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1003; 9019</t>
+          <t>934; 8751</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4084; 14967</t>
+          <t>4270; 15677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2037; 11603</t>
+          <t>2064; 11831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 12394</t>
+          <t>0; 11612</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2393; 11140</t>
+          <t>2323; 10197</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1903; 10680</t>
+          <t>1809; 10553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6074</t>
+          <t>0; 5962</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>921; 10742</t>
+          <t>1006; 10652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2192; 11938</t>
+          <t>2012; 11732</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1944; 11275</t>
+          <t>1885; 10864</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1786; 10271</t>
+          <t>1844; 9772</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 8127</t>
+          <t>0; 10183</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6846; 19361</t>
+          <t>6416; 18920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5524; 17516</t>
+          <t>5466; 17202</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2723; 12319</t>
+          <t>2779; 12442</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2664; 14929</t>
+          <t>2803; 16177</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2904; 10951</t>
+          <t>3016; 11027</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6780; 19881</t>
+          <t>6843; 19492</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5252; 15305</t>
+          <t>5348; 15359</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1564; 10490</t>
+          <t>1648; 10149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2737; 12324</t>
+          <t>2670; 11258</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11268; 25819</t>
+          <t>10412; 24768</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3457; 14762</t>
+          <t>3605; 14476</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4651; 12919</t>
+          <t>4349; 12926</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7464; 19717</t>
+          <t>8066; 19481</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20739; 39199</t>
+          <t>21148; 40560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11506; 25848</t>
+          <t>11438; 27499</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7300; 19281</t>
+          <t>8248; 20263</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>954; 8247</t>
+          <t>966; 8635</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8709; 19999</t>
+          <t>8209; 19701</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4696; 14234</t>
+          <t>5218; 15017</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8646; 21007</t>
+          <t>8376; 20594</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5355; 15740</t>
+          <t>5021; 14950</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17580; 32507</t>
+          <t>18374; 32926</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9382; 20535</t>
+          <t>8512; 20679</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8715; 16781</t>
+          <t>8627; 16738</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8109; 20129</t>
+          <t>8116; 19753</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30846; 48853</t>
+          <t>30269; 48572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16958; 32338</t>
+          <t>16865; 31613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19542; 34425</t>
+          <t>19263; 34570</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4384; 12502</t>
+          <t>4470; 11738</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4126; 14756</t>
+          <t>5093; 14625</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9936; 21648</t>
+          <t>8609; 21270</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10795; 23253</t>
+          <t>11290; 23765</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6498; 16546</t>
+          <t>6910; 16984</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7374; 17964</t>
+          <t>6753; 17746</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6865; 17714</t>
+          <t>6901; 17515</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5486; 12566</t>
+          <t>5150; 12673</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14151; 26611</t>
+          <t>13770; 26228</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13897; 28546</t>
+          <t>13688; 28729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19503; 35151</t>
+          <t>21260; 35838</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18739; 33136</t>
+          <t>18941; 33759</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1782; 10425</t>
+          <t>1787; 10361</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4998; 15677</t>
+          <t>5353; 16327</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4093; 14307</t>
+          <t>4358; 14831</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10034; 19526</t>
+          <t>10029; 19214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5498; 15451</t>
+          <t>5352; 14633</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6914; 17065</t>
+          <t>6117; 17027</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7886; 18817</t>
+          <t>7499; 18874</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2186; 7783</t>
+          <t>2579; 8159</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9342; 21435</t>
+          <t>9082; 21821</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14140; 28640</t>
+          <t>14247; 29948</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14796; 30035</t>
+          <t>14833; 30378</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14134; 25140</t>
+          <t>14271; 25085</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>811; 6754</t>
+          <t>824; 6982</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2081; 13194</t>
+          <t>2078; 13818</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2348; 10418</t>
+          <t>2252; 10186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3301; 10742</t>
+          <t>3228; 10581</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2071; 11543</t>
+          <t>2157; 11183</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2343; 12466</t>
+          <t>3132; 13226</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5011; 18009</t>
+          <t>4983; 17485</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6240; 14035</t>
+          <t>6521; 14130</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3935; 14782</t>
+          <t>3916; 14582</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6927; 21418</t>
+          <t>7482; 22408</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9632; 25063</t>
+          <t>10181; 24496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11797; 21832</t>
+          <t>11691; 21849</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25274; 45688</t>
+          <t>26122; 45854</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48081; 78523</t>
+          <t>49306; 78396</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42502; 66360</t>
+          <t>41819; 67203</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49639; 74594</t>
+          <t>50441; 74818</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38941; 62932</t>
+          <t>36755; 62079</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66124; 98443</t>
+          <t>66734; 98841</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51703; 79847</t>
+          <t>50800; 81415</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>39667; 60527</t>
+          <t>40092; 61718</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69951; 102057</t>
+          <t>71546; 102438</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>125411; 166042</t>
+          <t>122540; 167472</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>101246; 140920</t>
+          <t>102423; 142450</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>95101; 129204</t>
+          <t>96172; 129947</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 65,7</t>
+          <t>8,04; 66,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 58,98</t>
+          <t>7,87; 56,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,9</t>
+          <t>7,99; 52,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,08</t>
+          <t>0,0; 13,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 28,18</t>
+          <t>2,82; 26,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,86</t>
+          <t>0,0; 24,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,78</t>
+          <t>0,0; 55,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 22,75</t>
+          <t>2,52; 21,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 31,34</t>
+          <t>8,24; 30,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 26,12</t>
+          <t>4,52; 25,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,27</t>
+          <t>0,0; 47,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 43,63</t>
+          <t>8,55; 48,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 35,75</t>
+          <t>6,29; 35,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,85</t>
+          <t>0,0; 39,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 70,44</t>
+          <t>5,79; 66,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 16,0</t>
+          <t>2,94; 16,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 12,75</t>
+          <t>2,29; 12,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 16,11</t>
+          <t>3,02; 16,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,23</t>
+          <t>0,0; 20,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 19,57</t>
+          <t>6,46; 19,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 14,99</t>
+          <t>4,81; 16,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 16,82</t>
+          <t>3,69; 16,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 30,8</t>
+          <t>4,29; 28,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32,39%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>22,74%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32,39%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,88; 61,73</t>
+          <t>17,19; 61,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,39; 52,39</t>
+          <t>17,8; 52,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,03; 66,14</t>
+          <t>23,39; 67,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 47,54</t>
+          <t>9,66; 50,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 33,23</t>
+          <t>8,12; 35,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 44,31</t>
+          <t>20,49; 45,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 29,36</t>
+          <t>6,19; 28,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,16; 36,14</t>
+          <t>11,93; 33,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,59; 37,65</t>
+          <t>14,77; 37,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,71; 43,57</t>
+          <t>22,77; 43,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,77; 37,92</t>
+          <t>15,1; 35,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 35,48</t>
+          <t>13,72; 33,87</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 38,64</t>
+          <t>4,42; 38,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,91; 59,78</t>
+          <t>24,76; 60,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,28; 67,01</t>
+          <t>24,02; 66,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,35; 54,95</t>
+          <t>26,2; 56,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,42; 57,82</t>
+          <t>19,37; 56,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,11; 64,71</t>
+          <t>35,01; 64,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 65,51</t>
+          <t>27,2; 63,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,58; 57,38</t>
+          <t>32,55; 59,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 40,98</t>
+          <t>16,81; 42,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,1; 57,94</t>
+          <t>35,87; 58,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,25; 58,57</t>
+          <t>31,2; 58,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,9; 51,87</t>
+          <t>30,66; 53,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,97; 65,58</t>
+          <t>24,67; 66,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,4; 52,84</t>
+          <t>18,55; 53,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,26; 64,88</t>
+          <t>30,27; 66,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,23; 51,01</t>
+          <t>23,37; 48,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,01; 68,84</t>
+          <t>29,75; 68,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 60,28</t>
+          <t>22,06; 58,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 69,39</t>
+          <t>27,01; 70,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,71; 43,57</t>
+          <t>19,53; 46,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,35; 61,61</t>
+          <t>31,47; 60,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,96; 50,3</t>
+          <t>25,6; 50,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 61,76</t>
+          <t>35,43; 62,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,03; 44,61</t>
+          <t>26,06; 43,63</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,81; 45,31</t>
+          <t>7,51; 42,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,2; 55,5</t>
+          <t>18,44; 55,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,89; 40,48</t>
+          <t>11,45; 40,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,46; 54,52</t>
+          <t>27,18; 54,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,21; 49,78</t>
+          <t>20,92; 52,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 50,71</t>
+          <t>17,99; 47,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,66; 64,57</t>
+          <t>26,73; 65,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,55; 36,53</t>
+          <t>10,75; 36,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,38; 41,75</t>
+          <t>18,5; 42,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,62; 47,54</t>
+          <t>22,51; 46,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,52; 46,12</t>
+          <t>22,31; 45,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,79; 43,57</t>
+          <t>23,94; 42,26</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 35,79</t>
+          <t>4,18; 35,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,74; 38,19</t>
+          <t>5,79; 39,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,33; 46,75</t>
+          <t>10,78; 46,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,47; 34,33</t>
+          <t>10,06; 34,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 33,99</t>
+          <t>6,41; 34,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 29,85</t>
+          <t>7,26; 28,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,28; 43,1</t>
+          <t>14,15; 48,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,91; 34,48</t>
+          <t>16,34; 35,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 27,82</t>
+          <t>7,61; 27,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,3; 27,84</t>
+          <t>8,36; 26,59</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 39,29</t>
+          <t>15,66; 40,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,28; 30,43</t>
+          <t>16,4; 31,93</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,22</t>
+          <t>19,75; 33,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,73; 37,73</t>
+          <t>23,42; 37,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,74; 41,36</t>
+          <t>26,65; 42,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,82; 39,78</t>
+          <t>26,74; 39,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,8; 25,0</t>
+          <t>15,55; 25,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,95; 29,55</t>
+          <t>20,11; 29,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 30,21</t>
+          <t>19,59; 30,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,49; 28,46</t>
+          <t>18,47; 29,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,71; 26,79</t>
+          <t>18,4; 26,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,6; 30,88</t>
+          <t>23,22; 30,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,97</t>
+          <t>23,57; 32,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,75; 32,09</t>
+          <t>24,16; 32,08</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>820; 6649</t>
+          <t>814; 6720</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1211; 8734</t>
+          <t>1165; 8368</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6527</t>
+          <t>986; 6480</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6261</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1023; 9923</t>
+          <t>993; 9189</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7536</t>
+          <t>0; 8037</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 12777</t>
+          <t>0; 14483</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>934; 8751</t>
+          <t>970; 8334</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4270; 15677</t>
+          <t>4123; 15014</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2064; 11831</t>
+          <t>2050; 11612</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 11612</t>
+          <t>0; 12905</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7757</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2323; 10197</t>
+          <t>1998; 11240</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1809; 10553</t>
+          <t>1857; 10409</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5962</t>
+          <t>0; 5220</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1006; 10652</t>
+          <t>982; 11277</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2012; 11732</t>
+          <t>2154; 11812</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1885; 10864</t>
+          <t>1951; 10885</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1844; 9772</t>
+          <t>1830; 10276</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 10183</t>
+          <t>0; 8666</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6416; 18920</t>
+          <t>6251; 19192</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5466; 17202</t>
+          <t>5523; 18468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2779; 12442</t>
+          <t>2730; 12269</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2803; 16177</t>
+          <t>2573; 17110</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>14745</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3016; 11027</t>
+          <t>3070; 11031</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6843; 19492</t>
+          <t>6621; 19678</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5348; 15359</t>
+          <t>5431; 15699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1648; 10149</t>
+          <t>2309; 12050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2670; 11258</t>
+          <t>2752; 12121</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10412; 24768</t>
+          <t>11452; 25453</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3605; 14476</t>
+          <t>3053; 14182</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4349; 12926</t>
+          <t>4886; 13769</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8066; 19481</t>
+          <t>7643; 19227</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21148; 40560</t>
+          <t>21203; 40480</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11438; 27499</t>
+          <t>10953; 26025</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8248; 20263</t>
+          <t>8897; 21961</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>32128</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>966; 8635</t>
+          <t>987; 8646</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8209; 19701</t>
+          <t>8160; 20061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5218; 15017</t>
+          <t>5384; 14965</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8376; 20594</t>
+          <t>11137; 24137</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5021; 14950</t>
+          <t>5008; 14536</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18374; 32926</t>
+          <t>17814; 33061</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8512; 20679</t>
+          <t>8587; 19919</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8627; 16738</t>
+          <t>10583; 19394</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8116; 19753</t>
+          <t>8103; 20675</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30269; 48572</t>
+          <t>30070; 48855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16865; 31613</t>
+          <t>16843; 31746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19263; 34570</t>
+          <t>23001; 40274</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>28636</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4470; 11738</t>
+          <t>4415; 11834</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5093; 14625</t>
+          <t>5134; 14705</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8609; 21270</t>
+          <t>9925; 21809</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11290; 23765</t>
+          <t>11678; 24319</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6910; 16984</t>
+          <t>7339; 16958</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6753; 17746</t>
+          <t>6494; 17235</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6901; 17515</t>
+          <t>6817; 17806</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5150; 12673</t>
+          <t>6486; 15307</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13770; 26228</t>
+          <t>13395; 25869</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13688; 28729</t>
+          <t>14622; 28817</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21260; 35838</t>
+          <t>20559; 36260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18941; 33759</t>
+          <t>21678; 36290</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20709</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1787; 10361</t>
+          <t>1718; 9687</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5353; 16327</t>
+          <t>5425; 16200</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4358; 14831</t>
+          <t>4195; 14736</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10029; 19214</t>
+          <t>10285; 20474</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5352; 14633</t>
+          <t>6151; 15347</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6117; 17027</t>
+          <t>6040; 16100</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7499; 18874</t>
+          <t>7813; 19019</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2579; 8159</t>
+          <t>2755; 9317</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9082; 21821</t>
+          <t>9672; 22441</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14247; 29948</t>
+          <t>14179; 29029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14833; 30378</t>
+          <t>14694; 29976</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14271; 25085</t>
+          <t>15198; 26827</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17900</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>824; 6982</t>
+          <t>816; 6923</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2078; 13818</t>
+          <t>2096; 14353</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2252; 10186</t>
+          <t>2348; 10073</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3228; 10581</t>
+          <t>3287; 11137</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2157; 11183</t>
+          <t>2110; 11280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3132; 13226</t>
+          <t>3218; 12729</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4983; 17485</t>
+          <t>5739; 19516</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6521; 14130</t>
+          <t>7203; 15650</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3916; 14582</t>
+          <t>3987; 14233</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7482; 22408</t>
+          <t>6729; 21398</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10181; 24496</t>
+          <t>9762; 24941</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11691; 21849</t>
+          <t>12589; 24511</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26122; 45854</t>
+          <t>26457; 45426</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>49306; 78396</t>
+          <t>48660; 77457</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41819; 67203</t>
+          <t>43294; 68491</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50441; 74818</t>
+          <t>54867; 81090</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36755; 62079</t>
+          <t>38624; 63528</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66734; 98841</t>
+          <t>67275; 99595</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50800; 81415</t>
+          <t>52809; 81571</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>40092; 61718</t>
+          <t>45331; 71653</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71546; 102438</t>
+          <t>70362; 102503</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>122540; 167472</t>
+          <t>125932; 166310</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>102423; 142450</t>
+          <t>101805; 140282</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>96172; 129947</t>
+          <t>108858; 144554</t>
         </is>
       </c>
     </row>
